--- a/docs/EduSaldo - Plantilla Gestión Requerimientos.xlsx
+++ b/docs/EduSaldo - Plantilla Gestión Requerimientos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="572">
   <si>
     <t>ID</t>
   </si>
@@ -36,19 +36,43 @@
     <t>Prioridad</t>
   </si>
   <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>EP01</t>
+  </si>
+  <si>
+    <t>Tienda pública y navegación del establecimiento</t>
+  </si>
+  <si>
+    <t>Home, Blog, detalle de Blog, Cómo funciona, consentimiento de datos y derechos del titular.</t>
+  </si>
+  <si>
+    <t>Permitir que los apoderados conozcan el establecimiento y accedan a las páginas informativas y al login.</t>
+  </si>
+  <si>
     <t>Historia</t>
   </si>
   <si>
-    <t>Estado</t>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
   </si>
   <si>
     <t>Como</t>
   </si>
   <si>
-    <t>Responsable</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
+    <t>Florencia Soto</t>
+  </si>
+  <si>
+    <t>Cubre HU01, HU02, HU04, HU05, HU06, HU09 y HU76 a HU81. Home y Cómo funciona en Sprint 2; definición de producto en Sprint 1; consentimiento y derechos ARCO en Sprint 4.</t>
   </si>
   <si>
     <t>Quiero</t>
@@ -57,282 +81,258 @@
     <t>Para</t>
   </si>
   <si>
-    <t>EP01</t>
+    <t>EP02</t>
+  </si>
+  <si>
+    <t>Alta de cuentas, autenticación y perfiles</t>
+  </si>
+  <si>
+    <t>Alta de usuarios desde administración, selección de ubicación, inicio y cierre de sesión, perfiles de acceso y cambio de contraseña temporal.</t>
+  </si>
+  <si>
+    <t>Permitir identificar a los usuarios y controlar el acceso según los perfiles Administrador, Vendedor y Cliente.</t>
   </si>
   <si>
     <t>Sprint</t>
   </si>
   <si>
+    <t>Antonio Jara</t>
+  </si>
+  <si>
     <t>Criterios de Aceptación</t>
   </si>
   <si>
-    <t>Tienda pública y navegación del establecimiento</t>
-  </si>
-  <si>
-    <t>Home, Nosotros, Blog, detalle de Blog, Cómo funciona, consentimiento de datos y derechos del titular.</t>
-  </si>
-  <si>
-    <t>Permitir que los apoderados conozcan el establecimiento y accedan a las páginas informativas y al login.</t>
+    <t>Alta centralizada en el administrador (sin autorregistro público). Perfiles y cambio de contraseña en Sprint 3.</t>
+  </si>
+  <si>
+    <t>EP03</t>
+  </si>
+  <si>
+    <t>Catálogo, carrito y reserva de productos</t>
   </si>
   <si>
     <t>Review</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>Florencia Soto</t>
-  </si>
-  <si>
-    <t>Cubre HU01 a HU09 y HU76 a HU81. Home y Cómo funciona en Sprint 2; definición de producto en Sprint 1; consentimiento y derechos ARCO en Sprint 4.</t>
+    <t>Visualización del catálogo autenticado, detalle de productos, carrito y flujo de reserva de materiales.</t>
+  </si>
+  <si>
+    <t>Permitir al apoderado explorar productos, preparar su compra y reservar materiales para retiro presencial.</t>
+  </si>
+  <si>
+    <t>Pamela Acuña</t>
+  </si>
+  <si>
+    <t>Cubre HU17 a HU24. HU17-HU18 en Sprint 2. HU23-HU24 en Sprint 4. HU19-HU22 migran a E2 (Sprint 7, carrito TypeScript).</t>
+  </si>
+  <si>
+    <t>EP04</t>
+  </si>
+  <si>
+    <t>Contacto y comunicación</t>
+  </si>
+  <si>
+    <t>Formulario de contacto con validaciones.</t>
   </si>
   <si>
     <t>HU48</t>
   </si>
   <si>
+    <t>Facilitar la comunicación con la librería mediante un formulario validado.</t>
+  </si>
+  <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>EP07</t>
   </si>
   <si>
-    <t>EP02</t>
-  </si>
-  <si>
-    <t>Registro, autenticación y perfiles</t>
-  </si>
-  <si>
     <t>Trabajar de forma colaborativa en GitHub</t>
   </si>
   <si>
-    <t>Registro, selección de ubicación, inicio y cierre de sesión, perfiles de acceso y cambio de contraseña temporal.</t>
+    <t>Cubre HU25. Estructura en Sprint 2.</t>
   </si>
   <si>
     <t>Equipo de desarrollo</t>
   </si>
   <si>
-    <t>Permitir identificar a los usuarios y controlar el acceso según los perfiles Administrador, Vendedor y Cliente.</t>
+    <t>EP05</t>
   </si>
   <si>
     <t>Gestionar el código del proyecto en un repositorio compartido</t>
   </si>
   <si>
+    <t>Administración de productos y operación de librería</t>
+  </si>
+  <si>
     <t>Dejar evidencia del trabajo colaborativo exigido por la rúbrica</t>
   </si>
   <si>
-    <t>Antonio Jara</t>
-  </si>
-  <si>
-    <t>Cubre HU10 a HU16. Estructura en Sprint 2; perfiles y cambio de contraseña en Sprint 3.</t>
-  </si>
-  <si>
-    <t>EP03</t>
+    <t>Mantenedor de productos con control de stock, operación de reservas y registro de ventas diarias.</t>
+  </si>
+  <si>
+    <t>Mantener organizada la información del catálogo y ejecutar la operación diaria de la librería.</t>
   </si>
   <si>
     <t>Sprint 01</t>
   </si>
   <si>
-    <t>Catálogo, carrito y reserva de productos</t>
+    <t>Cubre HU26 a HU37. Home admin y home librería en Sprint 2; mantenedores y operación en Sprint 3.</t>
   </si>
   <si>
     <t>CA1: Dado el proyecto, cuando se revisa el repositorio, entonces todos los integrantes registran commits propios. CA2: Dado un commit, cuando se revisa su mensaje, entonces describe el cambio realizado de forma comprensible. CA3: Dado el repositorio, cuando se revisa su estructura, entonces incluye un README con la descripción del proyecto y los integrantes. CA4: Dado un avance de una funcionalidad, cuando se integra, entonces se realiza mediante una rama y su correspondiente fusión a la rama principal.</t>
   </si>
   <si>
-    <t>Visualización del catálogo autenticado, detalle de productos, carrito y flujo de reserva de materiales.</t>
-  </si>
-  <si>
-    <t>Permitir al apoderado explorar productos, preparar su compra y reservar materiales para retiro presencial.</t>
-  </si>
-  <si>
-    <t>Pamela Acuña</t>
-  </si>
-  <si>
-    <t>Cubre HU17 a HU24. HU17-HU18 en Sprint 2. HU23-HU24 en Sprint 4. HU19-HU22 migran a E2 (Sprint 7, carrito TypeScript).</t>
+    <t>EP06</t>
+  </si>
+  <si>
+    <t>Administración de usuarios y permisos</t>
+  </si>
+  <si>
+    <t>Mantenedor de usuarios, asignación de perfiles e importación de nómina.</t>
+  </si>
+  <si>
+    <t>Controlar los datos de usuarios y agilizar la carga inicial de estudiantes.</t>
   </si>
   <si>
     <t>Transversal. Repositorio configurado en Sprint 1.</t>
   </si>
   <si>
-    <t>EP04</t>
+    <t>Cubre HU38 a HU43. Todos en Sprint 3.</t>
+  </si>
+  <si>
+    <t>Experiencia, calidad y colaboración</t>
+  </si>
+  <si>
+    <t>HTML semántico, CSS externo, diseño responsivo, validaciones JavaScript, trabajo colaborativo en GitHub, migración a React y testing.</t>
   </si>
   <si>
     <t>HU76</t>
   </si>
   <si>
-    <t>Contacto y comunicación</t>
-  </si>
-  <si>
-    <t>Formulario de contacto con validaciones.</t>
+    <t>Asegurar un frontend mantenible, adaptable, verificado y desarrollado colaborativamente conforme a la rúbrica.</t>
   </si>
   <si>
     <t>Definir los actores del sistema</t>
   </si>
   <si>
-    <t>Facilitar la comunicación con la librería mediante un formulario validado.</t>
-  </si>
-  <si>
-    <t>Media</t>
+    <t>Cubre HU44 a HU48 y HU82 a HU85. HU45 en Sprint 2; HU46-HU47 en Sprint 3; HU44 y HU48 en Sprint 4; HU82 en Sprint 5; HU83 en Sprint 6; HU84 en Sprint 9; HU85 en Sprint 10.</t>
   </si>
   <si>
     <t>Identificar y documentar los actores del sistema</t>
   </si>
   <si>
+    <t>EP08</t>
+  </si>
+  <si>
     <t>Delimitar los roles que interactúan con EduSaldo</t>
   </si>
   <si>
-    <t>Cubre HU25. Estructura en Sprint 2.</t>
+    <t>Gestión de saldos escolares</t>
+  </si>
+  <si>
+    <t>Registro de estudiantes, asociación con apoderados, compras presenciales, control de stock y trazabilidad de movimientos.</t>
+  </si>
+  <si>
+    <t>Digitalizar y dar trazabilidad a los fondos que los apoderados destinan a sus pupilos.</t>
   </si>
   <si>
     <t>CA1: Dado el inicio del proyecto, cuando el equipo lo analiza, entonces documenta los actores Administrador, Vendedor, Apoderado y Visitante. CA2: Dado cada actor, cuando se documenta, entonces se describe su objetivo principal y sus funciones permitidas. CA3: Dado el conjunto de actores, cuando se revisa el ERS, entonces cada uno aparece con nombre, descripción y responsabilidades.</t>
   </si>
   <si>
-    <t>EP05</t>
-  </si>
-  <si>
-    <t>Administración de productos y operación de librería</t>
-  </si>
-  <si>
-    <t>Mantenedor de productos con control de stock, operación de reservas y registro de ventas diarias.</t>
-  </si>
-  <si>
-    <t>Mantener organizada la información del catálogo y ejecutar la operación diaria de la librería.</t>
+    <t>Cubre HU49 a HU54. Todos en Sprint 3. La parte visible del apoderado vive en EP10.</t>
+  </si>
+  <si>
+    <t>EP09</t>
+  </si>
+  <si>
+    <t>Búsqueda y filtrado del catálogo</t>
+  </si>
+  <si>
+    <t>Búsqueda por texto, filtros por precio, año escolar, materia y disponibilidad, combinación, limpieza, orden y persistencia.</t>
+  </si>
+  <si>
+    <t>Permitir al apoderado encontrar el material que necesita dentro del catálogo.</t>
   </si>
   <si>
     <t>Entregable del Sprint 1.</t>
   </si>
   <si>
-    <t>Cubre HU26 a HU37. Home admin y home librería en Sprint 2; mantenedores y operación en Sprint 3.</t>
+    <t>Cubre HU55 a HU67. Todos en Sprint 4. Lógica compartida en assets/js/filtros.js.</t>
   </si>
   <si>
     <t>HU77</t>
   </si>
   <si>
+    <t>EP10</t>
+  </si>
+  <si>
+    <t>Aportes del apoderado mediante pasarela de pago</t>
+  </si>
+  <si>
+    <t>Registro de aportes con Webpay, acreditación automática de saldo al pupilo, conciliación de transacciones huérfanas y control de acceso a datos.</t>
+  </si>
+  <si>
     <t>Definir el alcance del producto</t>
   </si>
   <si>
-    <t>EP06</t>
-  </si>
-  <si>
-    <t>Administración de usuarios y permisos</t>
+    <t>Dar transparencia y automatización al apoderado sobre el dinero que aporta y cómo lo usa cada uno de sus pupilos.</t>
   </si>
   <si>
     <t>Documentar el alcance del proyecto</t>
   </si>
   <si>
-    <t>Mantenedor de usuarios, asignación de perfiles e importación de nómina.</t>
+    <t>Cubre HU68 a HU75. HU75 y HU70-HU72 en Sprint 8; HU68, HU69 y HU74 en Sprint 11; HU73 en Sprint 12.</t>
   </si>
   <si>
     <t>Delimitar qué se construye en E1 y qué queda para E2/E3</t>
   </si>
   <si>
-    <t>Controlar los datos de usuarios y agilizar la carga inicial de estudiantes.</t>
-  </si>
-  <si>
     <t>CA1: Dado el inicio del proyecto, cuando el equipo lo analiza, entonces documenta los módulos incluidos en E1. CA2: Dado el alcance definido, cuando se revisa el ERS, entonces cada módulo tiene una descripción de límites y exclusiones. CA3: Dado el alcance, cuando se compara con el backlog, entonces no hay HUs fuera de los módulos declarados.</t>
   </si>
   <si>
-    <t>Cubre HU38 a HU43. Todos en Sprint 3.</t>
-  </si>
-  <si>
-    <t>Experiencia, calidad y colaboración</t>
-  </si>
-  <si>
-    <t>HTML semántico, CSS externo, diseño responsivo, validaciones JavaScript, trabajo colaborativo en GitHub, migración a React y testing.</t>
-  </si>
-  <si>
     <t>HU78</t>
   </si>
   <si>
-    <t>Asegurar un frontend mantenible, adaptable, verificado y desarrollado colaborativamente conforme a la rúbrica.</t>
-  </si>
-  <si>
     <t>Construir el Product Backlog priorizado</t>
   </si>
   <si>
-    <t>Cubre HU44 a HU48 y HU82 a HU85. HU45 en Sprint 2; HU46-HU47 en Sprint 3; HU44 y HU48 en Sprint 4; HU82 en Sprint 5; HU83 en Sprint 6; HU84 en Sprint 9; HU85 en Sprint 10.</t>
-  </si>
-  <si>
     <t>Construir y priorizar el backlog</t>
   </si>
   <si>
     <t>Contar con la lista ordenada de HUs que guiará los sprints</t>
   </si>
   <si>
-    <t>EP08</t>
-  </si>
-  <si>
-    <t>Gestión de saldos escolares</t>
-  </si>
-  <si>
     <t>CA1: Dado el análisis del dominio, cuando el equipo lo redacta, entonces existe un backlog con todas las HUs del proyecto. CA2: Dado el backlog, cuando se prioriza, entonces cada HU tiene un valor Alta, Media o Baja justificado. CA3: Dado el backlog, cuando se revisa, entonces las HUs están agrupadas por épica con identificadores únicos.</t>
   </si>
   <si>
-    <t>Registro de estudiantes, asociación con apoderados, compras presenciales, control de stock y trazabilidad de movimientos.</t>
-  </si>
-  <si>
-    <t>Digitalizar y dar trazabilidad a los fondos que los apoderados destinan a sus pupilos.</t>
-  </si>
-  <si>
-    <t>Cubre HU49 a HU54. Todos en Sprint 3. La parte visible del apoderado vive en EP10.</t>
-  </si>
-  <si>
     <t>HU79</t>
   </si>
   <si>
     <t>Redactar criterios de aceptación verificables</t>
   </si>
   <si>
-    <t>EP09</t>
-  </si>
-  <si>
-    <t>Búsqueda y filtrado del catálogo</t>
-  </si>
-  <si>
     <t>Redactar criterios de aceptación en formato BDD</t>
   </si>
   <si>
-    <t>Búsqueda por texto, filtros por precio, año escolar, materia y disponibilidad, combinación, limpieza, orden y persistencia.</t>
-  </si>
-  <si>
     <t>Permitir que cada criterio se traduzca en un test</t>
   </si>
   <si>
-    <t>Permitir al apoderado encontrar el material que necesita dentro del catálogo.</t>
-  </si>
-  <si>
     <t>CA1: Dado una HU del backlog, cuando el equipo redacta su criterio, entonces usa el formato Dado-Cuando-Entonces. CA2: Dado el criterio redactado, cuando se revisa, entonces contiene resultado observable y verificable. CA3: Dado el conjunto de criterios, cuando se auditan, entonces no hay criterios ambiguos ni juicios de valor.</t>
   </si>
   <si>
-    <t>Cubre HU55 a HU67. Todos en Sprint 4. Lógica compartida en assets/js/filtros.js.</t>
-  </si>
-  <si>
-    <t>EP10</t>
-  </si>
-  <si>
     <t>HU80</t>
   </si>
   <si>
-    <t>Aportes del apoderado mediante pasarela de pago</t>
-  </si>
-  <si>
-    <t>Registro de aportes con Webpay, acreditación automática de saldo al pupilo, conciliación de transacciones huérfanas y control de acceso a datos.</t>
-  </si>
-  <si>
     <t>Redactar la Especificación de Requisitos</t>
   </si>
   <si>
-    <t>Dar transparencia y automatización al apoderado sobre el dinero que aporta y cómo lo usa cada uno de sus pupilos.</t>
-  </si>
-  <si>
     <t>Redactar la ERS inicial del proyecto</t>
   </si>
   <si>
     <t>Dejar formalizado el análisis de requisitos</t>
   </si>
   <si>
-    <t>Cubre HU68 a HU75. HU75 y HU70-HU72 en Sprint 8; HU68, HU69 y HU74 en Sprint 11; HU73 en Sprint 12.</t>
-  </si>
-  <si>
     <t>CA1: Dado el análisis del dominio, cuando el equipo lo documenta, entonces existe un archivo ERS con actores, alcance, requisitos funcionales y no funcionales. CA2: Dado el ERS, cuando se revisa, entonces cada requisito tiene un identificador y una descripción verificable. CA3: Dado el ERS, cuando se compara con el backlog, entonces ambos son consistentes.</t>
   </si>
   <si>
@@ -393,73 +393,55 @@
     <t>Header inyectado vía header-footer.js. Estructura en Sprint 2.</t>
   </si>
   <si>
-    <t>HU03</t>
-  </si>
-  <si>
-    <t>Consultar el propósito de EduSaldo</t>
+    <t>HU04</t>
+  </si>
+  <si>
+    <t>Visualizar el listado del Blog</t>
+  </si>
+  <si>
+    <t>Visualizar el listado de noticias del Blog</t>
+  </si>
+  <si>
+    <t>Mantenerme informado sobre contenidos relacionados con la tienda</t>
+  </si>
+  <si>
+    <t>CA1: Dado un visitante en el menú principal, cuando selecciona Blog, entonces visualiza las noticias en formato de lista. CA2: Dado que existen noticias publicadas, cuando se carga el listado, entonces cada noticia muestra imagen, título y descripción corta. CA3: Dado que existen más de diez noticias, cuando se carga el listado, entonces se muestran diez por página con controles de paginación. CA4: Dado un conjunto de noticias con distintas fechas, cuando se carga el listado, entonces aparecen ordenadas de más reciente a más antigua. CA5: Dado una noticia del listado, cuando el visitante la selecciona, entonces accede a su vista de detalle.</t>
+  </si>
+  <si>
+    <t>pages/publico/blog.html. Estructura en Sprint 2.</t>
+  </si>
+  <si>
+    <t>HU05</t>
+  </si>
+  <si>
+    <t>Consultar el detalle de una noticia</t>
+  </si>
+  <si>
+    <t>Consultar el detalle de una noticia del Blog</t>
+  </si>
+  <si>
+    <t>Leer el contenido completo de un artículo publicado</t>
+  </si>
+  <si>
+    <t>CA1: Dado una noticia del listado, cuando el visitante selecciona ver detalle, entonces visualiza su imagen, título y descripción extensa. CA2: Dado que el sitio debe cumplir la pauta, cuando se revisa el proyecto, entonces existen al menos dos vistas de detalle de Blog construidas. CA3: Dado un visitante en el detalle de una noticia, cuando selecciona volver, entonces regresa al listado del Blog o a la página principal.</t>
+  </si>
+  <si>
+    <t>pages/publico/blog-detalle.html. Estructura en Sprint 2.</t>
+  </si>
+  <si>
+    <t>HU09</t>
+  </si>
+  <si>
+    <t>Consultar cómo funciona EduSaldo</t>
   </si>
   <si>
     <t>Visitante / Apoderado</t>
   </si>
   <si>
-    <t>Consultar información sobre el centro de apoderados</t>
-  </si>
-  <si>
-    <t>Comprender el propósito del centro y su rol en la librería escolar</t>
-  </si>
-  <si>
-    <t>CA1: Dado un visitante en cualquier página pública, cuando selecciona la opción Nosotros del menú, entonces accede a la vista Nosotros. CA2: Dado que la vista Nosotros está cargada, cuando el visitante la lee, entonces encuentra explicado el propósito del centro de apoderados y su coordinación con la librería escolar. CA3: Dado que la vista Nosotros está cargada, cuando se compara con el resto del sitio, entonces mantiene la misma paleta, tipografía y estructura. CA4: Dado que la vista Nosotros está cargada, cuando el visitante la recorre, entonces no encuentra referencias al equipo de desarrollo del software.</t>
-  </si>
-  <si>
-    <t>pages/publico/nosotros.html. Estructura en Sprint 2.</t>
-  </si>
-  <si>
-    <t>HU04</t>
-  </si>
-  <si>
-    <t>Visualizar el listado del Blog</t>
-  </si>
-  <si>
-    <t>Visualizar el listado de noticias del Blog</t>
-  </si>
-  <si>
-    <t>Mantenerme informado sobre contenidos relacionados con la tienda</t>
-  </si>
-  <si>
-    <t>CA1: Dado un visitante en el menú principal, cuando selecciona Blog, entonces visualiza las noticias en formato de lista. CA2: Dado que existen noticias publicadas, cuando se carga el listado, entonces cada noticia muestra imagen, título y descripción corta. CA3: Dado que existen más de diez noticias, cuando se carga el listado, entonces se muestran diez por página con controles de paginación. CA4: Dado un conjunto de noticias con distintas fechas, cuando se carga el listado, entonces aparecen ordenadas de más reciente a más antigua. CA5: Dado una noticia del listado, cuando el visitante la selecciona, entonces accede a su vista de detalle.</t>
-  </si>
-  <si>
-    <t>pages/publico/blog.html. Estructura en Sprint 2.</t>
-  </si>
-  <si>
-    <t>HU05</t>
-  </si>
-  <si>
-    <t>Consultar el detalle de una noticia</t>
-  </si>
-  <si>
-    <t>Consultar el detalle de una noticia del Blog</t>
-  </si>
-  <si>
-    <t>Leer el contenido completo de un artículo publicado</t>
-  </si>
-  <si>
-    <t>CA1: Dado una noticia del listado, cuando el visitante selecciona ver detalle, entonces visualiza su imagen, título y descripción extensa. CA2: Dado que el sitio debe cumplir la pauta, cuando se revisa el proyecto, entonces existen al menos dos vistas de detalle de Blog construidas. CA3: Dado un visitante en el detalle de una noticia, cuando selecciona volver, entonces regresa al listado del Blog o a la página principal.</t>
-  </si>
-  <si>
-    <t>pages/publico/blog-detalle.html. Estructura en Sprint 2.</t>
-  </si>
-  <si>
-    <t>HU09</t>
-  </si>
-  <si>
-    <t>Consultar cómo funciona EduSaldo</t>
-  </si>
-  <si>
     <t>Consultar cómo funciona la plataforma</t>
   </si>
   <si>
-    <t>Entender su funcionamiento antes de registrarme</t>
+    <t>Entender su funcionamiento antes de usar la plataforma</t>
   </si>
   <si>
     <t>Baja</t>
@@ -474,19 +456,22 @@
     <t>HU10</t>
   </si>
   <si>
-    <t>Registrar una cuenta de apoderado</t>
-  </si>
-  <si>
-    <t>Registrarme en EduSaldo</t>
-  </si>
-  <si>
-    <t>Disponer de una cuenta para utilizar las funcionalidades permitidas</t>
-  </si>
-  <si>
-    <t>CA1: Dado el formulario de registro, cuando el usuario ingresa un RUN sin puntos ni guion de 7 a 9 caracteres con dígito verificador válido, entonces el campo se acepta. CA2: Dado el formulario de registro, cuando el usuario deja vacío el RUN o ingresa uno inválido, entonces el sistema muestra un mensaje específico junto al campo y no permite continuar. CA3: Dado el formulario de registro, cuando el usuario ingresa un nombre de hasta 50 caracteres y apellidos de hasta 100, entonces los campos se aceptan. CA4: Dado el formulario de registro, cuando el usuario ingresa un correo de hasta 100 caracteres con dominio duoc.cl, profesor.duoc.cl o gmail.com, entonces el campo se acepta; en caso contrario se rechaza. CA5: Dado el formulario de registro, cuando el usuario ingresa una dirección de hasta 300 caracteres, entonces el campo se acepta. CA6: Dado un formulario con todos los datos válidos, cuando el usuario confirma el registro, entonces el sistema crea la cuenta y muestra la confirmación.</t>
-  </si>
-  <si>
-    <t>pages/acceso/registro.html. Estructura HTML en Sprint 2.</t>
+    <t>Registrar la cuenta de un apoderado</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>Crear la cuenta de un apoderado desde el panel administrativo</t>
+  </si>
+  <si>
+    <t>Habilitar el acceso de un apoderado que no quedó en la nómina inicial</t>
+  </si>
+  <si>
+    <t>CA1: Dado el formulario de alta de apoderado, cuando el administrador ingresa el RUN en cualquiera de sus formatos (con o sin puntos, con o sin guion, con o sin dígito verificador) y el RUN es válido, entonces el campo se acepta. CA2: Dado el formulario de alta de apoderado, cuando el RUN está vacío, contiene caracteres inválidos o presenta un dígito verificador incorrecto, entonces el sistema impide guardar. CA3: Dado el formulario de alta de apoderado, cuando el administrador ingresa un nombre de hasta 50 caracteres y apellidos de hasta 100, entonces los campos se aceptan. CA4: Dado el formulario de alta de apoderado, cuando el administrador ingresa un correo de hasta 100 caracteres con formato válido, entonces el campo se acepta. CA5: Dado el formulario de alta de apoderado, cuando el administrador ingresa un correo con formato inválido, entonces el sistema lo rechaza con un mensaje específico. CA6: Dado el formulario de alta de apoderado, cuando el administrador ingresa una dirección de hasta 300 caracteres, entonces el campo se acepta. CA7: Dado el formulario de alta de apoderado, cuando falta el correo, la dirección, la región o la comuna, entonces el sistema impide guardar y marca los campos pendientes. CA8: Dado el formulario de alta de apoderado, cuando se carga, entonces no existe ningún campo para definir la contraseña. CA9: Dado un formulario con datos válidos, cuando el administrador confirma el alta, entonces el sistema crea la cuenta con perfil Cliente, genera una contraseña temporal y la envía al correo registrado. CA10: Dado el apoderado creado, cuando inicia sesión por primera vez, entonces el sistema lo obliga a cambiar la contraseña y a registrar su consentimiento según HU15 y HU06.</t>
+  </si>
+  <si>
+    <t>Alta de apoderados desde pages/administrador/usuario-crear.html. Sustituye el autorregistro público.</t>
   </si>
   <si>
     <t>HU11</t>
@@ -495,19 +480,16 @@
     <t>Seleccionar la región de residencia</t>
   </si>
   <si>
-    <t>Cliente / Apoderado / Administrador</t>
-  </si>
-  <si>
-    <t>Seleccionar la región de mi residencia</t>
-  </si>
-  <si>
-    <t>Registrar correctamente mi ubicación</t>
-  </si>
-  <si>
-    <t>CA1: Dado un formulario con dirección, cuando se carga la página, entonces el selector de región se llena desde un arreglo JavaScript. CA2: Dado el selector de región, cuando el usuario elige una región, entonces el campo se acepta y se habilita el selector de comuna.</t>
-  </si>
-  <si>
-    <t>Aplica en registro y en formulario administrativo de usuario. Estructura en Sprint 2.</t>
+    <t>Seleccionar la región de residencia del usuario</t>
+  </si>
+  <si>
+    <t>Registrar correctamente su ubicación</t>
+  </si>
+  <si>
+    <t>CA1: Dado el formulario administrativo de usuario, cuando se carga la página, entonces el selector de región se llena desde un arreglo JavaScript. CA2: Dado el selector de región, cuando el administrador elige una región, entonces el campo se acepta y se habilita el selector de comuna.</t>
+  </si>
+  <si>
+    <t>Aplica en el formulario administrativo de usuario (pages/administrador/usuarios.html).</t>
   </si>
   <si>
     <t>HU12</t>
@@ -522,7 +504,7 @@
     <t>Registrar una ubicación sin combinaciones inválidas</t>
   </si>
   <si>
-    <t>CA1: Dado el selector de región con una región seleccionada, cuando se carga, entonces el selector de comunas se recarga solo con las comunas de esa región. CA2: Dado que el usuario ya eligió una comuna, cuando cambia de región, entonces la comuna previamente seleccionada se limpia. CA3: Dado un formulario enviado, cuando la comuna no pertenece a la región seleccionada, entonces el sistema rechaza el envío con un mensaje específico.</t>
+    <t>CA1: Dado el selector de región con una región seleccionada, cuando se carga, entonces el selector de comunas se recarga solo con las comunas de esa región. CA2: Dado que el administrador ya eligió una comuna, cuando cambia de región, entonces la comuna previamente seleccionada se limpia. CA3: Dado un formulario enviado, cuando la comuna no pertenece a la región seleccionada, entonces el sistema rechaza el envío con un mensaje específico.</t>
   </si>
   <si>
     <t>HU13</t>
@@ -540,7 +522,7 @@
     <t>Acceder a las funciones correspondientes a mi perfil</t>
   </si>
   <si>
-    <t>CA1: Dado el formulario de login, cuando el usuario ingresa un correo de hasta 100 caracteres con dominio duoc.cl, profesor.duoc.cl o gmail.com, entonces el campo se acepta. CA2: Dado el formulario de login, cuando el usuario ingresa una contraseña de entre 4 y 10 caracteres, entonces el campo se acepta. CA3: Dado un formulario de login, cuando los datos son inválidos o están incompletos, entonces el sistema muestra un mensaje específico por campo y no procesa el envío. CA4: Dado un usuario registrado, cuando ingresa credenciales válidas, entonces el sistema permite el acceso y lo dirige al área correspondiente a su perfil.</t>
+    <t>CA1: Dado el formulario de login, cuando el usuario ingresa un correo de hasta 100 caracteres con formato válido, entonces el campo se acepta. CA2: Dado el formulario de login, cuando el usuario ingresa una contraseña de entre 4 y 10 caracteres, entonces el campo se acepta. CA3: Dado un formulario de login, cuando los datos son inválidos o están incompletos, entonces el sistema muestra un mensaje específico por campo y no procesa el envío. CA4: Dado un usuario registrado, cuando ingresa credenciales válidas, entonces el sistema permite el acceso y lo dirige al área correspondiente a su perfil.</t>
   </si>
   <si>
     <t>pages/acceso/login.html. Estructura en Sprint 2.</t>
@@ -594,7 +576,7 @@
     <t>Comunicar una duda, comentario o solicitud a la librería</t>
   </si>
   <si>
-    <t>CA1: Dado el formulario de contacto, cuando el usuario ingresa un nombre de hasta 100 caracteres, entonces el campo se acepta. CA2: Dado el formulario de contacto, cuando el usuario ingresa un correo de hasta 100 caracteres con dominio permitido, entonces el campo se acepta; en caso contrario se rechaza. CA3: Dado el formulario de contacto, cuando el usuario ingresa un comentario de hasta 500 caracteres, entonces el campo se acepta. CA4: Dado un formulario con datos inválidos, cuando el usuario intenta enviarlo, entonces el sistema impide el procesamiento y muestra un mensaje específico junto a cada campo con error. CA5: Dado un formulario con datos válidos, cuando el usuario lo envía, entonces el sistema confirma que la consulta fue recibida.</t>
+    <t>CA1: Dado el formulario de contacto, cuando el usuario ingresa un nombre de hasta 100 caracteres, entonces el campo se acepta. CA2: Dado el formulario de contacto, cuando el usuario ingresa un correo de hasta 100 caracteres con formato válido, entonces el campo se acepta; en caso contrario se rechaza. CA3: Dado el formulario de contacto, cuando el usuario ingresa un comentario de hasta 500 caracteres, entonces el campo se acepta. CA4: Dado un formulario con datos inválidos, cuando el usuario intenta enviarlo, entonces el sistema impide el procesamiento y muestra un mensaje específico junto a cada campo con error. CA5: Dado un formulario con datos válidos, cuando el usuario lo envía, entonces el sistema confirma que la consulta fue recibida.</t>
   </si>
   <si>
     <t>pages/publico/contacto.html. Estructura en Sprint 2.</t>
@@ -606,9 +588,6 @@
     <t>Acceder al Home administrativo</t>
   </si>
   <si>
-    <t>Administrador</t>
-  </si>
-  <si>
     <t>Acceder al Home del sistema administrativo</t>
   </si>
   <si>
@@ -924,19 +903,19 @@
     <t>HU39</t>
   </si>
   <si>
-    <t>Crear un usuario</t>
-  </si>
-  <si>
-    <t>Crear usuarios desde el panel administrativo</t>
-  </si>
-  <si>
-    <t>Incorporar nuevas cuentas con su perfil correspondiente</t>
-  </si>
-  <si>
-    <t>CA1: Dado el formulario de usuario, cuando el administrador ingresa un RUN sin puntos ni guion de 7 a 9 caracteres con dígito verificador válido, entonces el campo se acepta. CA2: Dado el formulario de usuario, cuando ingresa un nombre de hasta 50 caracteres y apellidos de hasta 100, entonces los campos se aceptan. CA3: Dado el formulario de usuario, cuando ingresa un correo de hasta 100 caracteres con dominio permitido, entonces el campo se acepta. CA4: Dado el formulario de usuario, cuando ingresa una fecha de nacimiento o la deja vacía, entonces el campo se acepta por ser opcional. CA5: Dado el formulario de usuario, cuando ingresa una dirección de hasta 300 caracteres, entonces el campo se acepta. CA6: Dado el formulario de usuario, cuando no selecciona un tipo de usuario, entonces el sistema impide guardar y muestra un mensaje específico. CA7: Dado el formulario de usuario, cuando se carga, entonces no existe ningún campo para que el administrador defina la contraseña. CA8: Dado un formulario con datos válidos, cuando el administrador confirma el registro, entonces el sistema genera automáticamente una contraseña temporal y el usuario queda disponible en el listado. CA9: Dado una contraseña temporal generada, cuando se crea el usuario, entonces el sistema la muestra al administrador una sola vez y la envía al correo registrado. CA10: Dado un usuario creado, cuando inicia sesión con la contraseña temporal, entonces el sistema lo obliga a cambiarla según HU15. CA11: Dado un formulario con datos inválidos, cuando intenta guardar, entonces el sistema muestra un mensaje personalizado junto a cada campo con error.</t>
-  </si>
-  <si>
-    <t>Modal de creación dentro del listado de usuarios. Vista en Sprint 3.</t>
+    <t>Crear un usuario de staff</t>
+  </si>
+  <si>
+    <t>Crear cuentas de Administrador o Vendedor desde el panel administrativo</t>
+  </si>
+  <si>
+    <t>Incorporar al personal con su perfil correspondiente</t>
+  </si>
+  <si>
+    <t>CA1: Dado el formulario de usuario, cuando el administrador ingresa el RUN en cualquiera de sus formatos (con o sin puntos, con o sin guion, con o sin dígito verificador) y el RUN es válido, entonces el campo se acepta. CA2: Dado el formulario de usuario, cuando ingresa un nombre de hasta 50 caracteres y apellidos de hasta 100, entonces los campos se aceptan. CA3: Dado el formulario de usuario, cuando ingresa un correo de hasta 100 caracteres con formato válido, entonces el campo se acepta. CA4: Dado el formulario de usuario, cuando ingresa una fecha de nacimiento o la deja vacía, entonces el campo se acepta por ser opcional. CA5: Dado el formulario de usuario, cuando ingresa una dirección de hasta 300 caracteres, entonces el campo se acepta. CA6: Dado el formulario de usuario, cuando no selecciona un tipo de usuario entre Administrador y Vendedor, entonces el sistema impide guardar y muestra un mensaje específico. CA7: Dado el formulario de usuario, cuando se carga, entonces no existe ningún campo para que el administrador defina la contraseña. CA8: Dado un formulario con datos válidos, cuando el administrador confirma el registro, entonces el sistema genera automáticamente una contraseña temporal y el usuario queda disponible en el listado. CA9: Dado una contraseña temporal generada, cuando se crea el usuario, entonces el sistema la muestra al administrador una sola vez y la envía al correo registrado. CA10: Dado un usuario creado, cuando inicia sesión con la contraseña temporal, entonces el sistema lo obliga a cambiarla según HU15. CA11: Dado un formulario con datos inválidos, cuando intenta guardar, entonces el sistema muestra un mensaje personalizado junto a cada campo con error.</t>
+  </si>
+  <si>
+    <t>Alta de cuentas de staff en pages/administrador/usuario-crear.html. La creación de apoderados (Cliente) corresponde a HU10.</t>
   </si>
   <si>
     <t>HU40</t>
@@ -1164,10 +1143,10 @@
     <t>Sprint 04</t>
   </si>
   <si>
-    <t>CA1: Dado el formulario de registro, cuando el apoderado lo completa, entonces existe un checkbox obligatorio que describe la finalidad del tratamiento de datos. CA2: Dado un apoderado que marca el checkbox, cuando confirma el registro, entonces el sistema registra el consentimiento con fecha y versión del aviso de privacidad. CA3: Dado un apoderado registrado, cuando accede a su perfil, entonces puede revocar el consentimiento. CA4: Dado un apoderado que revoca el consentimiento, cuando el sistema procesa la revocación, entonces anonimiza sus datos personales y los de sus pupilos en un plazo no mayor a 30 días.</t>
-  </si>
-  <si>
-    <t>Checkbox en pages/acceso/registro.html. Validación JS en Sprint 4.</t>
+    <t>CA1: Dado el primer inicio de sesión de un apoderado con contraseña temporal, cuando el sistema muestra la pantalla de cambio de contraseña, entonces presenta un checkbox obligatorio que describe la finalidad del tratamiento de datos. CA2: Dado que el apoderado marca el checkbox, cuando confirma el cambio de contraseña, entonces el sistema registra el consentimiento con fecha y versión del aviso de privacidad y habilita el acceso a la información de sus pupilos. CA3: Dado un apoderado que no marca el checkbox, cuando intenta continuar, entonces el sistema impide el acceso hasta que otorgue el consentimiento. CA4: Dado un apoderado registrado, cuando accede a su perfil, entonces puede revocar el consentimiento. CA5: Dado un apoderado que revoca el consentimiento, cuando el sistema procesa la revocación, entonces anonimiza sus datos personales y los de sus pupilos en un plazo no mayor a 30 días.</t>
+  </si>
+  <si>
+    <t>Checkbox obligatorio en el primer ingreso (pages/acceso/cambiar-contrasena.html) antes de acceder a datos de pupilos. Revocación en pages/apoderado/perfil.html.</t>
   </si>
   <si>
     <t>HU07</t>
@@ -1521,8 +1500,7 @@
     <t>CA1: Dado un producto disponible, cuando el apoderado selecciona agregar al carrito, entonces el producto se incorpora con cantidad inicial uno. CA2: Dado un producto ya presente en el carrito, cuando el apoderado lo agrega nuevamente, entonces el sistema incrementa su cantidad en lugar de crear una segunda línea. CA3: Dado un producto agregado, cuando se actualiza el carrito, entonces este muestra su nombre, precio y cantidad. CA4: Dado un producto agregado, cuando se actualiza el carrito, entonces el contador visible refleja la cantidad total de artículos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Migra a E2 (Sprint 7, carrito TypeScript).
-</t>
+    <t>Migra a E2 (Sprint 7, carrito TypeScript).</t>
   </si>
   <si>
     <t>HU20</t>
@@ -1648,8 +1626,7 @@
     <t>Escribir el primer conjunto de pruebas derivadas de HUs y criterios de aceptación</t>
   </si>
   <si>
-    <t xml:space="preserve">Asegurar que carrito formularios y componentes funcionan como se especificó
-</t>
+    <t>Asegurar que carrito formularios y componentes funcionan como se especificó</t>
   </si>
   <si>
     <t>Sprint 09</t>
@@ -2291,13 +2268,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
@@ -2320,28 +2297,28 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -2364,28 +2341,28 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -2408,28 +2385,28 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -2452,28 +2429,28 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -2496,28 +2473,28 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -2540,28 +2517,28 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -2584,28 +2561,28 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -2628,28 +2605,28 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -2672,28 +2649,28 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -2716,28 +2693,28 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -30499,37 +30476,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -30542,43 +30519,43 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
@@ -30591,43 +30568,43 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="I3" s="3" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
@@ -30640,43 +30617,43 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -30689,43 +30666,43 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -30738,43 +30715,43 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
@@ -30787,43 +30764,43 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>104</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
@@ -30839,13 +30816,13 @@
         <v>105</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>106</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>107</v>
@@ -30854,25 +30831,25 @@
         <v>108</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>109</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
@@ -30888,7 +30865,7 @@
         <v>110</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>111</v>
@@ -30903,7 +30880,7 @@
         <v>114</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>115</v>
@@ -30912,13 +30889,13 @@
         <v>116</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>117</v>
@@ -30937,7 +30914,7 @@
         <v>118</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>119</v>
@@ -30952,7 +30929,7 @@
         <v>121</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>115</v>
@@ -30961,13 +30938,13 @@
         <v>122</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>123</v>
@@ -30986,40 +30963,40 @@
         <v>124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>125</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="G11" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
@@ -31032,43 +31009,43 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>112</v>
       </c>
       <c r="E12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>134</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
@@ -31081,16 +31058,16 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>138</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>112</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>139</v>
@@ -31099,25 +31076,25 @@
         <v>140</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>50</v>
+        <v>141</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
@@ -31130,43 +31107,43 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
@@ -31179,43 +31156,43 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
@@ -31228,16 +31205,16 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>159</v>
@@ -31246,7 +31223,7 @@
         <v>160</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>115</v>
@@ -31255,16 +31232,16 @@
         <v>161</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
@@ -31277,16 +31254,16 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>165</v>
@@ -31295,7 +31272,7 @@
         <v>166</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>115</v>
@@ -31304,16 +31281,16 @@
         <v>167</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
@@ -31326,25 +31303,25 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>172</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>115</v>
@@ -31353,10 +31330,10 @@
         <v>173</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>33</v>
@@ -31378,22 +31355,22 @@
         <v>175</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>176</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>178</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>115</v>
@@ -31402,13 +31379,13 @@
         <v>179</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>180</v>
@@ -31433,7 +31410,7 @@
         <v>182</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>183</v>
@@ -31442,7 +31419,7 @@
         <v>184</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>115</v>
@@ -31451,13 +31428,13 @@
         <v>185</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>186</v>
@@ -31476,13 +31453,13 @@
         <v>187</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>188</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>189</v>
@@ -31491,7 +31468,7 @@
         <v>190</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>115</v>
@@ -31500,13 +31477,13 @@
         <v>191</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="M21" s="3" t="s">
         <v>192</v>
@@ -31525,7 +31502,7 @@
         <v>193</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>194</v>
@@ -31540,7 +31517,7 @@
         <v>197</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>115</v>
@@ -31549,13 +31526,13 @@
         <v>198</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>199</v>
@@ -31574,40 +31551,40 @@
         <v>200</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>201</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
@@ -31620,40 +31597,40 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>211</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>212</v>
@@ -31672,37 +31649,37 @@
         <v>213</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>214</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>218</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M25" s="3" t="s">
         <v>219</v>
@@ -31721,7 +31698,7 @@
         <v>220</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>221</v>
@@ -31730,31 +31707,31 @@
         <v>222</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>226</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
@@ -31767,40 +31744,40 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>230</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>231</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>232</v>
@@ -31819,40 +31796,40 @@
         <v>233</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>234</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="G28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
@@ -31865,43 +31842,43 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="J29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>245</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
@@ -31914,43 +31891,43 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>251</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
@@ -31963,43 +31940,43 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>257</v>
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
@@ -32012,43 +31989,43 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>263</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
@@ -32061,43 +32038,43 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>269</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
@@ -32110,43 +32087,43 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>271</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>275</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
@@ -32159,43 +32136,43 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I35" s="3" t="s">
+      <c r="J35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
@@ -32208,43 +32185,43 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I36" s="3" t="s">
+      <c r="J36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>287</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
@@ -32257,43 +32234,43 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I37" s="3" t="s">
+      <c r="J37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
@@ -32306,43 +32283,43 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I38" s="3" t="s">
+      <c r="J38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
@@ -32355,43 +32332,43 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E39" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I39" s="3" t="s">
+      <c r="J39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
@@ -32404,43 +32381,43 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E40" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="G40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="G40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I40" s="3" t="s">
+      <c r="J40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M40" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -32453,43 +32430,43 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E41" s="3" t="s">
+      <c r="F41" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I41" s="3" t="s">
+      <c r="J41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
@@ -32502,43 +32479,43 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E42" s="3" t="s">
+      <c r="F42" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="G42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I42" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I42" s="3" t="s">
+      <c r="J42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
@@ -32551,43 +32528,43 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E43" s="3" t="s">
+      <c r="F43" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
@@ -32600,43 +32577,43 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E44" s="3" t="s">
+      <c r="F44" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="F44" s="3" t="s">
+      <c r="G44" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M44" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
@@ -32649,43 +32626,43 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
@@ -32698,43 +32675,43 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="G46" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>346</v>
-      </c>
       <c r="J46" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
@@ -32747,43 +32724,43 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>195</v>
       </c>
       <c r="E47" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I47" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="J47" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M47" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
@@ -32796,43 +32773,43 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E48" s="3" t="s">
+      <c r="F48" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="G48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I48" s="3" t="s">
+      <c r="J48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M48" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
@@ -32845,43 +32822,43 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>363</v>
-      </c>
       <c r="J49" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
@@ -32894,43 +32871,43 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="J50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M50" s="3" t="s">
         <v>368</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>364</v>
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
@@ -32943,40 +32920,40 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="G51" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>374</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M51" s="3" t="s">
         <v>375</v>
@@ -32995,13 +32972,13 @@
         <v>376</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>377</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>378</v>
@@ -33010,25 +32987,25 @@
         <v>379</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H52" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I52" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M52" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>382</v>
       </c>
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
@@ -33041,43 +33018,43 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I53" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="G53" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>387</v>
-      </c>
       <c r="J53" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
@@ -33090,43 +33067,43 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="F54" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E54" s="3" t="s">
+      <c r="G54" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I54" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="J54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M54" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
@@ -33139,43 +33116,43 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="G55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G55" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I55" s="3" t="s">
+      <c r="J55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M55" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
@@ -33188,16 +33165,16 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>402</v>
@@ -33206,22 +33183,22 @@
         <v>403</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>404</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="M56" s="3" t="s">
         <v>405</v>
@@ -33240,40 +33217,40 @@
         <v>406</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>407</v>
       </c>
       <c r="D57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="G57" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I57" s="3" t="s">
+      <c r="J57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M57" s="3" t="s">
         <v>411</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>412</v>
       </c>
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
@@ -33286,43 +33263,43 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I58" s="3" t="s">
+      <c r="J58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>417</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>418</v>
       </c>
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
@@ -33335,43 +33312,43 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I59" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="J59" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
@@ -33384,43 +33361,43 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E60" s="3" t="s">
+      <c r="G60" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I60" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>429</v>
-      </c>
       <c r="J60" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
@@ -33433,43 +33410,43 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C61" s="3" t="s">
+      <c r="F61" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E61" s="3" t="s">
+      <c r="G61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="F61" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>434</v>
-      </c>
       <c r="J61" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
@@ -33482,43 +33459,43 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E62" s="3" t="s">
+      <c r="G62" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I62" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="J62" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
@@ -33531,43 +33508,43 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C63" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="G63" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I63" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="F63" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>444</v>
-      </c>
       <c r="J63" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
@@ -33580,43 +33557,43 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E64" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="F64" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E64" s="3" t="s">
+      <c r="G64" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I64" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>449</v>
-      </c>
       <c r="J64" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
@@ -33629,43 +33606,43 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="F65" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E65" s="3" t="s">
+      <c r="G65" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I65" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="J65" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
@@ -33678,43 +33655,43 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E66" s="3" t="s">
+      <c r="G66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I66" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>459</v>
-      </c>
       <c r="J66" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
@@ -33727,43 +33704,43 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E67" s="3" t="s">
+      <c r="G67" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>464</v>
-      </c>
       <c r="J67" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
@@ -33776,43 +33753,43 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="G68" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I68" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>469</v>
-      </c>
       <c r="J68" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
@@ -33825,43 +33802,43 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E69" s="3" t="s">
+      <c r="G69" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>474</v>
-      </c>
       <c r="J69" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
@@ -33874,43 +33851,43 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E70" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C70" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E70" s="3" t="s">
+      <c r="G70" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="G70" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="I70" s="3" t="s">
+      <c r="J70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L70" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="J70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="M70" s="3" t="s">
-        <v>424</v>
+        <v>480</v>
       </c>
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
@@ -33923,40 +33900,40 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="M71" s="3" t="s">
         <v>487</v>
@@ -33975,40 +33952,40 @@
         <v>488</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>489</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="E72" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F72" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="G72" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="J72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M72" s="3" t="s">
         <v>493</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="M72" s="3" t="s">
-        <v>494</v>
       </c>
       <c r="N72" s="5"/>
       <c r="O72" s="5"/>
@@ -34021,43 +33998,43 @@
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="F73" s="3" t="s">
+      <c r="G73" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="G73" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>499</v>
-      </c>
       <c r="J73" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="N73" s="5"/>
       <c r="O73" s="5"/>
@@ -34070,43 +34047,43 @@
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I74" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>504</v>
-      </c>
       <c r="J74" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="N74" s="5"/>
       <c r="O74" s="5"/>
@@ -34119,43 +34096,43 @@
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="G75" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="I75" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>508</v>
-      </c>
       <c r="J75" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
@@ -34168,43 +34145,43 @@
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="F76" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E76" s="3" t="s">
+      <c r="G76" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="I76" s="3" t="s">
+      <c r="J76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M76" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M76" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
@@ -34220,13 +34197,13 @@
         <v>514</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>515</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>516</v>
@@ -34235,25 +34212,25 @@
         <v>517</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H77" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="I77" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="J77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M77" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M77" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
@@ -34266,43 +34243,43 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="G78" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="I78" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="G78" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="I78" s="3" t="s">
+      <c r="J78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M78" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
@@ -34315,43 +34292,43 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E79" s="3" t="s">
+      <c r="F79" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="G79" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="I79" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="G79" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="I79" s="3" t="s">
+      <c r="J79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M79" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M79" s="3" t="s">
-        <v>532</v>
       </c>
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
@@ -34364,40 +34341,40 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E80" s="3" t="s">
+      <c r="F80" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="G80" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" s="3" t="s">
         <v>536</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>537</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>21</v>
+        <v>479</v>
       </c>
       <c r="M80" s="3" t="s">
         <v>538</v>
@@ -34416,13 +34393,13 @@
         <v>539</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>540</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>541</v>
@@ -34431,7 +34408,7 @@
         <v>542</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>543</v>
@@ -34440,13 +34417,13 @@
         <v>544</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="M81" s="3" t="s">
         <v>545</v>
@@ -34465,13 +34442,13 @@
         <v>546</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>547</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>548</v>
@@ -34480,7 +34457,7 @@
         <v>549</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>550</v>
@@ -34489,13 +34466,13 @@
         <v>551</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>486</v>
+        <v>16</v>
       </c>
       <c r="M82" s="3" t="s">
         <v>552</v>
@@ -34514,13 +34491,13 @@
         <v>553</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>554</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>555</v>
@@ -34529,25 +34506,25 @@
         <v>556</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="H83" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="I83" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="J83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M83" s="3" t="s">
         <v>558</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>559</v>
       </c>
       <c r="N83" s="5"/>
       <c r="O83" s="5"/>
@@ -34560,43 +34537,43 @@
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B84" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E84" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E84" s="3" t="s">
+      <c r="F84" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="G84" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="I84" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="G84" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="I84" s="3" t="s">
+      <c r="J84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K84" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L84" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M84" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="J84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M84" s="3" t="s">
-        <v>565</v>
       </c>
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
@@ -34609,40 +34586,40 @@
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B85" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="E85" s="3" t="s">
+      <c r="F85" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="G85" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>557</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>570</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K85" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L85" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M85" s="3" t="s">
         <v>571</v>
@@ -34658,43 +34635,43 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K86" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M86" s="3" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>

--- a/docs/EduSaldo - Plantilla Gestión Requerimientos.xlsx
+++ b/docs/EduSaldo - Plantilla Gestión Requerimientos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\30 - Studies\01 - Ingeniería en Informática\Semestre 04\DSY1104 - Desarrollo Fullstack II\EduSaldo\paginaWeb\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A41ED94-75B0-45AB-98DA-604459CE66B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC93677-4043-480A-ABF5-36D7E9C28809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="453">
   <si>
     <t>ID</t>
   </si>
@@ -1260,6 +1260,144 @@
   <si>
     <t>CA1: Dado un alumno nuevo, cuando registra RUT válido y único, nombre, apellidos, curso y datos requeridos, entonces se crea con id interno y estado ACTIVO. CA2: Dado un RUT ya registrado, cuando intenta crear otro alumno, entonces el sistema impide el duplicado. CA3: Dado el alta, cuando se completa, entonces el Administrador puede asociarlo a una cuenta de apoderado o crear una nueva.</t>
   </si>
+  <si>
+    <t>CA1: Dado un usuario con historial, cuando se inactiva, entonces no puede iniciar sesión y sus operaciones históricas permanecen consultables. CA2: Dado una cuenta inactiva que puede volver a operar, cuando el Administrador la reactiva, entonces recupera acceso según su estado de seguridad.</t>
+  </si>
+  <si>
+    <t>Se elimina CA3: la regla ya está en HU66 CA1.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un archivo válido, cuando se carga, entonces el sistema muestra una previsualización con cantidad de alumnos, apoderados nuevos, apoderados existentes, asociaciones nuevas y errores. CA2: Dado un RUT de alumno ya existente, cuando se procesa, entonces no se duplica el alumno. CA3: Dado un RUT de Apoderado ya existente, y un nuevo alumno, cuando se ingresa, entonces se crea una nueva asociación apoderado-alumno. CA4: Dada información contradictoria para un mismo RUT, cuando se valida, entonces el registro queda pendiente de revisión y no se sobrescribe automáticamente. CA5: Dado la confirmación final, cuando se importa, entonces se crean los registros válidos y las cuentas nuevas quedan PRIMER_ACCESO con contraseña temporal. CA6: Dado una fila sin un apoderado válido, cuando se valida, entonces queda marcada como ERROR y no se crea el alumno.</t>
+  </si>
+  <si>
+    <t>Alineada a relación N:M; ningún alumno sin apoderado.</t>
+  </si>
+  <si>
+    <t>Registrar un alumno con su apoderado</t>
+  </si>
+  <si>
+    <t>registrar un alumno junto con al menos un apoderado en una sola operación</t>
+  </si>
+  <si>
+    <t>que ningún alumno ni apoderado quede sin asociación</t>
+  </si>
+  <si>
+    <t>CA1: Dado un alumno nuevo con RUT válido y único, nombre, apellidos, fecha de nacimiento y curso, cuando el Administrador ingresa además los datos de un apoderado y su parentesco y confirma, entonces se crean el alumno en estado ACTIVO y la asociación apoderado-alumno en una sola operación. CA2: Dado un RUT de apoderado que no existe, cuando se confirma el alta, entonces se crea el usuario Apoderado con contraseña temporal y estado PRIMER_ACCESO. CA3: Dado un RUT de apoderado ya registrado, cuando se confirma el alta, entonces se reutiliza ese usuario y solo se crea la nueva asociación. CA4: Dado un RUT de alumno ya registrado o datos de alumno o apoderado inválidos, cuando intenta confirmar, entonces el sistema impide el alta y no crea ningún registro. CA5: Dado un fallo al crear el usuario Apoderado, cuando no puede completarse el alta, entonces no queda un alumno sin apoderado ni un apoderado sin alumno.</t>
+  </si>
+  <si>
+    <t>Fusiona ex-HU04 (creación de apoderado). Asociación obligatoria.</t>
+  </si>
+  <si>
+    <t>HU16</t>
+  </si>
+  <si>
+    <t>Agregar o desvincular apoderados de un alumno</t>
+  </si>
+  <si>
+    <t>asociar un apoderado adicional a un alumno existente o desvincular uno</t>
+  </si>
+  <si>
+    <t>mantener actualizada la relación entre apoderados y alumnos con trazabilidad</t>
+  </si>
+  <si>
+    <t>CA1: Dado un alumno ACTIVO, cuando el Administrador le asocia otro apoderado (nuevo o existente por RUT) indicando parentesco, entonces se crea la asociación y el alumno queda visible desde la cuenta de ese apoderado. CA2: Dado un apoderado ya asociado a ese alumno, cuando se intenta asociarlo nuevamente, entonces el sistema impide duplicar la asociación. CA3: Dado una asociación vigente, cuando el Administrador la desvincula indicando un motivo obligatorio, entonces queda DESVINCULADA con fecha, responsable y motivo, sin eliminarse. CA4: Dado un alumno ACTIVO con un único apoderado vigente, cuando se intenta desvincular ese apoderado sin asociar otro, entonces el sistema lo impide. CA5: Dado varios apoderados asociados a un alumno, cuando cualquiera de ellos consulta, entonces todos ven el mismo saldo, movimientos, reservas y compras del alumno.</t>
+  </si>
+  <si>
+    <t>Recrea HU16 para la relación N:M.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un alumno con reservas pendientes o saldo por resolver, cuando se intenta inactivar, entonces el sistema advierte las situaciones pendientes. CA2: Dado un alumno INACTIVO, cuando se consulta desde la cuenta de su apoderado, entonces no permite nuevos abonos, reservas ni compras. CA3: Dada una cuenta de apoderado sin alumnos activos, cuando el Administrador lo decide, entonces puede inactivar también la cuenta. CA4: Dado un alumno inactivado, cuando se consulta su historial, entonces sus asociaciones con apoderados se conservan.</t>
+  </si>
+  <si>
+    <t>Agrega CA4: se conservan las asociaciones con apoderados.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un saldo disponible que pasa a ser igual o inferior al umbral configurado, inicialmente $3.000, cuando ocurre el cruce, entonces se envía un único correo y se activa un aviso persistente en la cuenta de todos los apoderados con asociación vigente. CA2: Dada una alerta activa, cuando el saldo continúa disminuyendo, entonces el aviso se actualiza pero no se envían nuevos correos. CA3: Dado un abono que eleva el saldo disponible sobre el umbral, cuando se procesa, entonces la alerta se resuelve y el aviso desaparece. CA4: Dado un nuevo descenso posterior al umbral, cuando ocurre, entonces comienza un nuevo ciclo y puede enviarse un nuevo correo.</t>
+  </si>
+  <si>
+    <t>CA1 precisa destinatarios: todos los apoderados con asociación vigente.</t>
+  </si>
+  <si>
+    <t>CA1: Dado una reserva LISTA_PARA_RETIRO, cuando confirma la entrega, entonces se crea la venta y su detalle y la reserva pasa a ENTREGADA. CA2: Dado la entrega, cuando se procesa, entonces el saldo comprometido se convierte en débito definitivo del saldo del alumno y se registra su movimiento. CA3: Dado la entrega, cuando se procesa, entonces el stock reservado se libera y el stock físico disminuye por las unidades entregadas. CA4: Dado un fallo en alguna parte del flujo, cuando no puede completarse consistentemente, entonces la reserva no queda marcada como ENTREGADA sin las compensaciones o confirmaciones correspondientes.</t>
+  </si>
+  <si>
+    <t>CA2: "egreso" reemplazado por "débito definitivo del saldo" (término de caja, HU54/HU58).</t>
+  </si>
+  <si>
+    <t>CA1: Dado un producto, cuando se consulta inventario, entonces muestra stock físico, stock reservado y stock disponible calculado como físico menos reservado. CA2: Dado movimientos de reserva, entrega, devolución o recepción, cuando se completan, entonces las magnitudes reflejan el último estado. CA3: Dado cualquier operación, cuando intentaría producir stock físico o disponible negativo, entonces el sistema la rechaza.</t>
+  </si>
+  <si>
+    <t>Recibe ex-CA3 de HU42 (stock físico o disponible negativo).</t>
+  </si>
+  <si>
+    <t>CA1: Dado un producto con stock crítico, cuando el stock disponible es igual o inferior al umbral, entonces aparece en el reporte/alerta de stock crítico. CA2: Dado una reposición que eleva el stock disponible sobre el umbral, cuando se actualiza, entonces deja de aparecer como crítico.</t>
+  </si>
+  <si>
+    <t>CA3 trasladado a HU41.</t>
+  </si>
+  <si>
+    <t>CA1: Dado una jornada de inventario, cuando se ingresan conteos físicos, entonces el sistema calcula diferencias frente al stock físico registrado. CA2: Dado el inventario capturado, cuando se finaliza, entonces puede imprimirse/exportarse como respaldo y conservar evidencia asociada. CA3: Dado diferencias detectadas, cuando se finaliza el conteo, entonces genera reportes de diferencia para el flujo de ajuste (HU45) y no modifica automáticamente el stock.</t>
+  </si>
+  <si>
+    <t>CA3: las diferencias alimentan el flujo de ajuste de HU45.</t>
+  </si>
+  <si>
+    <t>Reportar diferencias y autorizar ajustes de stock</t>
+  </si>
+  <si>
+    <t>reportar diferencias de stock y gestionar su ajuste con doble firma</t>
+  </si>
+  <si>
+    <t>corregir el inventario con trazabilidad y control</t>
+  </si>
+  <si>
+    <t>CA1: Dado una diferencia detectada en la operación diaria o en un inventario físico, cuando el Encargado la reporta, entonces queda registrado un reporte PENDIENTE con producto, cantidad, descripción y evidencia, sin modificar el stock. CA2: Dado un reporte pendiente, cuando el Administrador lo revisa, entonces puede descartarlo con motivo o crear la solicitud de ajuste con producto, cantidad, motivo y evidencia. CA3: Dado una solicitud de ajuste pendiente, cuando el Autorizador la aprueba, entonces se genera el movimiento de stock y queda trazabilidad del reporte, el solicitante y el aprobador. CA4: Dado una solicitud rechazada, cuando se procesa, entonces el stock no cambia. CA5: Dado un Encargado, cuando intenta crear o aprobar una solicitud de ajuste, entonces el sistema lo impide.</t>
+  </si>
+  <si>
+    <t>Encargado notifica; Administrador solicita; Autorizador aprueba.</t>
+  </si>
+  <si>
+    <t>CA1: Dado proveedor y productos válidos, cuando crea la OC, entonces registra cantidades, costo neto, IVA y total. CA2: Dado una OC emitida, cuando se consulta, entonces conserva sus valores originales y estado. CA3: Dado una OC, cuando aún no tiene recepción, entonces el Administrador puede cancelarla indicando un motivo obligatorio, y queda en estado CANCELADA con fecha y responsable.</t>
+  </si>
+  <si>
+    <t>CA3: cancelación por el Administrador con motivo obligatorio; estado CANCELADA.</t>
+  </si>
+  <si>
+    <t>Registrar la recepción de mercadería con su factura</t>
+  </si>
+  <si>
+    <t>recepcionar la mercadería de una OC comparando la orden, la factura y lo recibido</t>
+  </si>
+  <si>
+    <t>ingresar al stock solo mercadería respaldada por una factura que coincide</t>
+  </si>
+  <si>
+    <t>CA1: Dado una OC vigente, cuando llega mercadería con su factura, entonces el Encargado registra la factura (número, fecha, neto, IVA y total) y compara producto y cantidad contra la OC y la factura. CA2: Dado que la factura coincide exactamente con lo recibido, cuando confirma, entonces la recepción queda ACEPTADA como COMPLETA o INCOMPLETA, aumenta el stock físico por las unidades recibidas y se recalcula el CPP. CA3: Dado que la factura no coincide con la mercadería recibida, cuando se revisa, entonces la recepción completa queda RECHAZADA con motivo obligatorio y no modifica stock ni CPP. CA4: Dado una recepción INCOMPLETA aceptada, cuando quedan unidades pendientes, entonces la OC queda en RECEPCIÓN_PARCIAL y abierta para nuevas recepciones. CA5: Dado una OC con varias recepciones, cuando se consulta, entonces cada recepción muestra su propia factura, y la factura aceptada queda pendiente de pago en Finanzas.</t>
+  </si>
+  <si>
+    <t>Fusiona ex-HU50 y ex-HU53. Regla de la arquitectura: 1 factura por recepción; rechazo total si no coincide.</t>
+  </si>
+  <si>
+    <t>CA1: Dado el parámetro de saldo bajo, cuando se configura, entonces el valor inicial es $3.000 y puede modificarse por el Administrador. CA2: Dado el plazo de revisión mensual, cuando se configura, entonces el valor inicial es tres días calendario y se usa para el cierre automático. CA3: Dado un cambio de parámetro, cuando se guarda, entonces queda auditado y aplica hacia adelante. CA4: Dado el parámetro de edad mínima para venta directa, cuando se configura, entonces el valor inicial es 12 años y HU28 y HU34 lo usan para decidir entre reserva y venta directa.</t>
+  </si>
+  <si>
+    <t>Agrega CA4: parámetro de edad mínima para venta directa (12 años).</t>
+  </si>
+  <si>
+    <t>Usuarios, cuentas de apoderado y seguridad</t>
+  </si>
+  <si>
+    <t>Cambia "cuentas familiares" por "cuentas de apoderado".</t>
+  </si>
+  <si>
+    <t>CA1: Dado un alumno menor de 12 años asociado a la cuenta, saldo disponible suficiente y stock disponible suficiente, cuando confirma, entonces se crea una única reserva PENDIENTE con sus detalles (líneas de productos y cantidades comprometidas). CA2: Dado la reserva confirmada, cuando se registra, entonces aumenta saldo comprometido y stock reservado sin disminuir todavía el saldo actual ni el stock físico. CA3: Dado saldo o stock insuficiente, cuando intenta confirmar, entonces la operación completa se rechaza sin cambios parciales. CA4: Dado un alumno de 12 años o más, cuando se intenta generar reserva por esta vía, entonces el sistema informa que corresponde atención/entrega directa según la regla operativa vigente.</t>
+  </si>
+  <si>
+    <t>CA1: Dado una OC vigente, cuando llega mercadería con su factura, entonces el Encargado registra la factura (número, fecha, neto, IVA y total) y compara producto y cantidad contra la OC y la factura. CA2: Dado que la factura coincide exactamente con lo recibido, cuando confirma, entonces la recepción queda ACEPTADA como COMPLETA o INCOMPLETA, aumenta el stock físico por las unidades recibidas y se recalcula el CPP. CA3: Dado que la factura no coincide con la mercadería recibida o contiene artículos no ordenados, cuando se revisa, entonces la recepción puntual queda RECHAZADA con motivo obligatorio (junto con su factura), no modifica stock ni CPP, y la OC permanece vigente para un nuevo despacho. CA4: Dado una recepción INCOMPLETA aceptada, cuando quedan unidades pendientes, entonces la OC queda en RECEPCIÓN_PARCIAL y abierta para nuevas recepciones. CA5: Dado una OC con varias recepciones, cuando se consulta, entonces cada recepción muestra su propia factura, y la factura aceptada queda pendiente de pago en Finanzas.</t>
+  </si>
+  <si>
+    <t>Fusiona ex-HU50 y ex-HU53. Regla: 1 factura por recepción; rechazo puntual de recepción/factura manteniendo la OC vigente; múltiples recepciones/facturas por OC.</t>
+  </si>
 </sst>
 </file>
 
@@ -1473,28 +1611,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <vertical style="thin">
-          <color rgb="FFD4D4D4"/>
-        </vertical>
-        <horizontal style="thin">
-          <color rgb="FFD4D4D4"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor theme="0"/>
@@ -1564,19 +1680,41 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <vertical style="thin">
+          <color rgb="FFD4D4D4"/>
+        </vertical>
+        <horizontal style="thin">
+          <color rgb="FFD4D4D4"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Epicas-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="18"/>
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="firstRowStripe" dxfId="20"/>
-      <tableStyleElement type="secondRowStripe" dxfId="19"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="21"/>
+      <tableStyleElement type="headerRow" dxfId="20"/>
+      <tableStyleElement type="firstRowStripe" dxfId="19"/>
+      <tableStyleElement type="secondRowStripe" dxfId="18"/>
     </tableStyle>
     <tableStyle name="Historias de Usuario-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="14"/>
-      <tableStyleElement type="headerRow" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="17"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="secondRowStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1922,7 +2060,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>20</v>
+        <v>451</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>21</v>
@@ -1936,7 +2074,9 @@
       <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>452</v>
+      </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -29137,24 +29277,24 @@
       <c r="T4" s="6"/>
       <c r="U4" s="5"/>
     </row>
-    <row r="5" spans="1:21" ht="100.8">
+    <row r="5" spans="1:21" ht="72">
       <c r="A5" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>398</v>
+        <v>71</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>399</v>
+        <v>72</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>400</v>
+        <v>73</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>23</v>
@@ -29163,7 +29303,7 @@
         <v>42</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>401</v>
+        <v>74</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>17</v>
@@ -29182,22 +29322,22 @@
     </row>
     <row r="6" spans="1:21" ht="72">
       <c r="A6" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>23</v>
@@ -29206,7 +29346,7 @@
         <v>42</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>17</v>
@@ -29223,24 +29363,24 @@
       <c r="T6" s="6"/>
       <c r="U6" s="5"/>
     </row>
-    <row r="7" spans="1:21" ht="72">
+    <row r="7" spans="1:21" ht="86.4">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>77</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>23</v>
@@ -29249,7 +29389,7 @@
         <v>42</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>17</v>
@@ -29266,24 +29406,24 @@
       <c r="T7" s="6"/>
       <c r="U7" s="5"/>
     </row>
-    <row r="8" spans="1:21" ht="86.4">
+    <row r="8" spans="1:21" ht="57.6">
       <c r="A8" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>23</v>
@@ -29292,7 +29432,7 @@
         <v>42</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>17</v>
@@ -29309,24 +29449,24 @@
       <c r="T8" s="6"/>
       <c r="U8" s="5"/>
     </row>
-    <row r="9" spans="1:21" ht="57.6">
+    <row r="9" spans="1:21" ht="72">
       <c r="A9" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>23</v>
@@ -29335,7 +29475,7 @@
         <v>42</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>17</v>
@@ -29352,24 +29492,24 @@
       <c r="T9" s="6"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="72">
+    <row r="10" spans="1:21" ht="86.4">
       <c r="A10" s="4" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>23</v>
@@ -29378,7 +29518,7 @@
         <v>42</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>17</v>
@@ -29397,22 +29537,22 @@
     </row>
     <row r="11" spans="1:21" ht="86.4">
       <c r="A11" s="4" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>23</v>
@@ -29421,7 +29561,7 @@
         <v>42</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>17</v>
@@ -29438,24 +29578,24 @@
       <c r="T11" s="6"/>
       <c r="U11" s="5"/>
     </row>
-    <row r="12" spans="1:21" ht="86.4">
+    <row r="12" spans="1:21" ht="57.6">
       <c r="A12" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>23</v>
@@ -29464,7 +29604,7 @@
         <v>42</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>17</v>
@@ -29483,22 +29623,22 @@
     </row>
     <row r="13" spans="1:21" ht="57.6">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>23</v>
@@ -29507,13 +29647,15 @@
         <v>42</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>112</v>
+        <v>410</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>411</v>
+      </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
@@ -29524,24 +29666,24 @@
       <c r="T13" s="6"/>
       <c r="U13" s="5"/>
     </row>
-    <row r="14" spans="1:21" ht="72">
+    <row r="14" spans="1:21" ht="158.4">
       <c r="A14" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>114</v>
+        <v>402</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>23</v>
@@ -29550,13 +29692,15 @@
         <v>42</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>117</v>
+        <v>412</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>413</v>
+      </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
@@ -29567,24 +29711,24 @@
       <c r="T14" s="6"/>
       <c r="U14" s="5"/>
     </row>
-    <row r="15" spans="1:21" ht="129.6">
+    <row r="15" spans="1:21" ht="158.4">
       <c r="A15" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>119</v>
+        <v>415</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>120</v>
+        <v>416</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>23</v>
@@ -29593,13 +29737,15 @@
         <v>42</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
+      <c r="L15" s="4" t="s">
+        <v>418</v>
+      </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
@@ -29610,24 +29756,24 @@
       <c r="T15" s="6"/>
       <c r="U15" s="5"/>
     </row>
-    <row r="16" spans="1:21" ht="72">
+    <row r="16" spans="1:21" ht="144">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>419</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>122</v>
+        <v>420</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>123</v>
+        <v>421</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>124</v>
+        <v>422</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>23</v>
@@ -29636,13 +29782,15 @@
         <v>42</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="L16" s="4" t="s">
+        <v>424</v>
+      </c>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
@@ -29696,7 +29844,7 @@
       <c r="T17" s="6"/>
       <c r="U17" s="5"/>
     </row>
-    <row r="18" spans="1:21" ht="72">
+    <row r="18" spans="1:21" ht="100.8">
       <c r="A18" s="4" t="s">
         <v>130</v>
       </c>
@@ -29722,13 +29870,15 @@
         <v>42</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
+      <c r="L18" s="4" t="s">
+        <v>426</v>
+      </c>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
@@ -29939,13 +30089,15 @@
         <v>42</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="L23" s="4" t="s">
+        <v>428</v>
+      </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
@@ -30154,7 +30306,7 @@
         <v>42</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>184</v>
+        <v>453</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>17</v>
@@ -30369,13 +30521,15 @@
         <v>42</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>210</v>
+        <v>429</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
+      <c r="L33" s="4" t="s">
+        <v>430</v>
+      </c>
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
@@ -30687,7 +30841,7 @@
       <c r="T40" s="6"/>
       <c r="U40" s="5"/>
     </row>
-    <row r="41" spans="1:21" ht="57.6">
+    <row r="41" spans="1:21" ht="72">
       <c r="A41" s="4" t="s">
         <v>247</v>
       </c>
@@ -30713,13 +30867,15 @@
         <v>42</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>252</v>
+        <v>431</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
+      <c r="L41" s="4" t="s">
+        <v>432</v>
+      </c>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
       <c r="O41" s="6"/>
@@ -30756,13 +30912,15 @@
         <v>42</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>257</v>
+        <v>433</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
+      <c r="L42" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
       <c r="O42" s="6"/>
@@ -30816,7 +30974,7 @@
       <c r="T43" s="6"/>
       <c r="U43" s="5"/>
     </row>
-    <row r="44" spans="1:21" ht="72">
+    <row r="44" spans="1:21" ht="86.4">
       <c r="A44" s="4" t="s">
         <v>263</v>
       </c>
@@ -30842,13 +31000,15 @@
         <v>42</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>267</v>
+        <v>435</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
+      <c r="L44" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
       <c r="O44" s="6"/>
@@ -30859,7 +31019,7 @@
       <c r="T44" s="6"/>
       <c r="U44" s="5"/>
     </row>
-    <row r="45" spans="1:21" ht="72">
+    <row r="45" spans="1:21" ht="144">
       <c r="A45" s="4" t="s">
         <v>268</v>
       </c>
@@ -30867,16 +31027,16 @@
         <v>40</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>269</v>
+        <v>437</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>270</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>271</v>
+        <v>438</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>272</v>
+        <v>439</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>23</v>
@@ -30885,13 +31045,15 @@
         <v>42</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>273</v>
+        <v>440</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
+      <c r="L45" s="4" t="s">
+        <v>441</v>
+      </c>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
       <c r="O45" s="6"/>
@@ -30945,7 +31107,7 @@
       <c r="T46" s="6"/>
       <c r="U46" s="5"/>
     </row>
-    <row r="47" spans="1:21" ht="57.6">
+    <row r="47" spans="1:21" ht="72">
       <c r="A47" s="4" t="s">
         <v>279</v>
       </c>
@@ -30971,13 +31133,15 @@
         <v>42</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>283</v>
+        <v>442</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
+      <c r="L47" s="4" t="s">
+        <v>443</v>
+      </c>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
       <c r="O47" s="6"/>
@@ -31031,7 +31195,7 @@
       <c r="T48" s="6"/>
       <c r="U48" s="5"/>
     </row>
-    <row r="49" spans="1:21" ht="72">
+    <row r="49" spans="1:21" ht="158.4">
       <c r="A49" s="4" t="s">
         <v>289</v>
       </c>
@@ -31039,16 +31203,16 @@
         <v>46</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>290</v>
+        <v>444</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>192</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>291</v>
+        <v>445</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>292</v>
+        <v>446</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>23</v>
@@ -31057,13 +31221,15 @@
         <v>42</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>293</v>
+        <v>454</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
+      <c r="L49" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
       <c r="O49" s="6"/>
@@ -31074,24 +31240,24 @@
       <c r="T49" s="6"/>
       <c r="U49" s="5"/>
     </row>
-    <row r="50" spans="1:21" ht="86.4">
+    <row r="50" spans="1:21" ht="72">
       <c r="A50" s="4" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>192</v>
+        <v>99</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>23</v>
@@ -31100,7 +31266,7 @@
         <v>42</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>17</v>
@@ -31119,22 +31285,22 @@
     </row>
     <row r="51" spans="1:21" ht="72">
       <c r="A51" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>23</v>
@@ -31143,7 +31309,7 @@
         <v>42</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>17</v>
@@ -31162,22 +31328,22 @@
     </row>
     <row r="52" spans="1:21" ht="72">
       <c r="A52" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>69</v>
+        <v>316</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>23</v>
@@ -31186,7 +31352,7 @@
         <v>42</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>17</v>
@@ -31205,22 +31371,22 @@
     </row>
     <row r="53" spans="1:21" ht="72">
       <c r="A53" s="4" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="D53" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>23</v>
@@ -31229,7 +31395,7 @@
         <v>42</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>17</v>
@@ -31246,24 +31412,24 @@
       <c r="T53" s="6"/>
       <c r="U53" s="5"/>
     </row>
-    <row r="54" spans="1:21" ht="72">
+    <row r="54" spans="1:21" ht="57.6">
       <c r="A54" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>23</v>
@@ -31272,7 +31438,7 @@
         <v>42</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>17</v>
@@ -31289,24 +31455,24 @@
       <c r="T54" s="6"/>
       <c r="U54" s="5"/>
     </row>
-    <row r="55" spans="1:21" ht="72">
+    <row r="55" spans="1:21" ht="57.6">
       <c r="A55" s="4" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>23</v>
@@ -31315,7 +31481,7 @@
         <v>42</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>17</v>
@@ -31332,24 +31498,24 @@
       <c r="T55" s="6"/>
       <c r="U55" s="5"/>
     </row>
-    <row r="56" spans="1:21" ht="57.6">
+    <row r="56" spans="1:21" ht="72">
       <c r="A56" s="4" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>327</v>
+        <v>69</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>23</v>
@@ -31358,7 +31524,7 @@
         <v>42</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>17</v>
@@ -31375,24 +31541,24 @@
       <c r="T56" s="6"/>
       <c r="U56" s="5"/>
     </row>
-    <row r="57" spans="1:21" ht="57.6">
+    <row r="57" spans="1:21" ht="72">
       <c r="A57" s="4" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>23</v>
@@ -31401,7 +31567,7 @@
         <v>42</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>17</v>
@@ -31418,24 +31584,24 @@
       <c r="T57" s="6"/>
       <c r="U57" s="5"/>
     </row>
-    <row r="58" spans="1:21" ht="72">
+    <row r="58" spans="1:21" ht="57.6">
       <c r="A58" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>23</v>
@@ -31444,7 +31610,7 @@
         <v>42</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>17</v>
@@ -31461,24 +31627,24 @@
       <c r="T58" s="6"/>
       <c r="U58" s="5"/>
     </row>
-    <row r="59" spans="1:21" ht="72">
+    <row r="59" spans="1:21" ht="100.8">
       <c r="A59" s="4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>69</v>
+        <v>353</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>23</v>
@@ -31487,7 +31653,7 @@
         <v>42</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>17</v>
@@ -31504,24 +31670,24 @@
       <c r="T59" s="6"/>
       <c r="U59" s="5"/>
     </row>
-    <row r="60" spans="1:21" ht="57.6">
+    <row r="60" spans="1:21" ht="86.4">
       <c r="A60" s="4" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>23</v>
@@ -31530,7 +31696,7 @@
         <v>42</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>17</v>
@@ -31547,24 +31713,24 @@
       <c r="T60" s="6"/>
       <c r="U60" s="5"/>
     </row>
-    <row r="61" spans="1:21" ht="100.8">
+    <row r="61" spans="1:21" ht="86.4">
       <c r="A61" s="4" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>353</v>
+        <v>69</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>23</v>
@@ -31573,7 +31739,7 @@
         <v>42</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>17</v>
@@ -31590,24 +31756,24 @@
       <c r="T61" s="6"/>
       <c r="U61" s="5"/>
     </row>
-    <row r="62" spans="1:21" ht="86.4">
+    <row r="62" spans="1:21" ht="100.8">
       <c r="A62" s="4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>23</v>
@@ -31616,13 +31782,15 @@
         <v>42</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>361</v>
+        <v>449</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
+      <c r="L62" s="4" t="s">
+        <v>450</v>
+      </c>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
       <c r="O62" s="6"/>
@@ -31633,24 +31801,24 @@
       <c r="T62" s="6"/>
       <c r="U62" s="5"/>
     </row>
-    <row r="63" spans="1:21" ht="86.4">
+    <row r="63" spans="1:21" ht="72">
       <c r="A63" s="4" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>23</v>
@@ -31659,7 +31827,7 @@
         <v>42</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>17</v>
@@ -31678,22 +31846,22 @@
     </row>
     <row r="64" spans="1:21" ht="86.4">
       <c r="A64" s="4" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>69</v>
+        <v>379</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>23</v>
@@ -31702,7 +31870,7 @@
         <v>42</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>17</v>
@@ -31719,24 +31887,24 @@
       <c r="T64" s="6"/>
       <c r="U64" s="5"/>
     </row>
-    <row r="65" spans="1:21" ht="72">
+    <row r="65" spans="1:21" ht="86.4">
       <c r="A65" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>69</v>
+        <v>385</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>23</v>
@@ -31745,7 +31913,7 @@
         <v>42</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>17</v>
@@ -31762,24 +31930,24 @@
       <c r="T65" s="6"/>
       <c r="U65" s="5"/>
     </row>
-    <row r="66" spans="1:21" ht="86.4">
+    <row r="66" spans="1:21" ht="72">
       <c r="A66" s="4" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B66" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>379</v>
+        <v>99</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>23</v>
@@ -31788,7 +31956,7 @@
         <v>42</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>382</v>
+        <v>407</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>17</v>
@@ -31805,33 +31973,33 @@
       <c r="T66" s="6"/>
       <c r="U66" s="5"/>
     </row>
-    <row r="67" spans="1:21" ht="86.4">
+    <row r="67" spans="1:21" ht="72">
       <c r="A67" s="4" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>385</v>
+        <v>136</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>17</v>
@@ -31848,39 +32016,19 @@
       <c r="T67" s="6"/>
       <c r="U67" s="5"/>
     </row>
-    <row r="68" spans="1:21" ht="72">
-      <c r="A68" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H68" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
+    <row r="68" spans="1:21">
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3"/>
+      <c r="L68" s="3"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
@@ -31891,39 +32039,19 @@
       <c r="T68" s="6"/>
       <c r="U68" s="5"/>
     </row>
-    <row r="69" spans="1:21" ht="72">
-      <c r="A69" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
+    <row r="69" spans="1:21">
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3"/>
+      <c r="L69" s="3"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
       <c r="O69" s="6"/>
@@ -53129,13 +53257,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="J70:J988" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J68:J988" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"Pendiente,Aprobada,Con observaciones,Rechazada"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="G2:G988" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J69" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J67" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Pendiente,Aprobado,Rechazado,No aplica"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/EduSaldo - Plantilla Gestión Requerimientos.xlsx
+++ b/docs/EduSaldo - Plantilla Gestión Requerimientos.xlsx
@@ -1398,6 +1398,66 @@
   <si>
     <t>Fusiona ex-HU50 y ex-HU53. Regla: 1 factura por recepción; rechazo puntual de recepción/factura manteniendo la OC vigente; múltiples recepciones/facturas por OC.</t>
   </si>
+  <si>
+    <t>CA1: Dado el formulario, cuando ingresa primer nombre, primer apellido, correo y mensaje válidos (segundo nombre y segundo apellido opcionales), entonces la consulta queda registrada o confirmada para envío. CA2: Dado datos inválidos, cuando intenta enviar, entonces el sistema informa los errores y no procesa la consulta.</t>
+  </si>
+  <si>
+    <t>Nombres atomizados en formulario de consulta.</t>
+  </si>
+  <si>
+    <t>CA1: Dado datos válidos de RUT, primer nombre, segundo nombre (opcional), primer apellido, segundo apellido (opcional), correo y rol, cuando el Administrador confirma, entonces se crea el usuario con contraseña temporal y PRIMER_ACCESO. CA2: Dado el rol seleccionado, cuando el usuario inicia sesión, entonces solo accede a las funciones autorizadas. CA3: Dado la creación, cuando se genera la contraseña temporal, entonces no se almacena ni expone en texto plano.</t>
+  </si>
+  <si>
+    <t>Nombres atomizados para usuarios de staff.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un alumno nuevo con RUT válido y único, primer nombre, segundo nombre (opcional), primer apellido, segundo apellido (opcional), fecha de nacimiento y curso, cuando el Administrador ingresa además los datos de un apoderado y su parentesco y confirma, entonces se crean el alumno en estado ACTIVO y la asociación apoderado-alumno en una sola operación. CA2: Dado un RUT de apoderado que no existe, cuando se confirma el alta, entonces se crea el usuario Apoderado con contraseña temporal y estado PRIMER_ACCESO. CA3: Dado un RUT de apoderado ya registrado, cuando se confirma el alta, entonces se reutiliza ese usuario y solo se crea la nueva asociación. CA4: Dado un RUT de alumno ya registrado o datos de alumno o apoderado inválidos, cuando intenta confirmar, entonces el sistema impide el alta y no crea ningún registro. CA5: Dado un fallo al crear el usuario Apoderado, cuando no puede completarse el alta, entonces no queda un alumno sin apoderado ni un apoderado sin alumno. CA6: Dado los datos del apoderado, cuando se ingresan, entonces se registran por separado primer nombre, segundo nombre (opcional), primer apellido y segundo apellido (opcional).</t>
+  </si>
+  <si>
+    <t>Fusiona ex-HU04 (creación de apoderado). Asociación obligatoria. Nombres atomizados para alumno y apoderado.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un alumno con reservas pendientes o saldo por resolver, cuando se intenta inactivar, entonces el sistema advierte las situaciones pendientes. CA2: Dado un alumno INACTIVO, cuando se consulta desde la cuenta de su apoderado, entonces no permite nuevos abonos, reservas ni compras. CA3: Dada una cuenta de apoderado sin alumnos activos, cuando el Administrador lo decide, entonces puede inactivar también la cuenta. CA4: Dado un alumno inactivado, cuando se consulta su historial, entonces sus asociaciones con apoderados se conservan. CA5: Dado un alumno con saldo disponible y sin reservas pendientes, cuando el Administrador registra la devolución de saldo indicando apoderado receptor, monto, medio (efectivo o transferencia), comprobante y motivo, entonces el saldo del alumno queda en cero con un movimiento DEVOLUCION_SALDO y se genera un único egreso en la Cuenta Librería. CA6: Dado un alumno con reservas pendientes, cuando se intenta registrar la devolución de saldo, entonces el sistema lo impide hasta cancelar o entregar esas reservas. CA7: Dado la devolución, cuando se registra, entonces la entrega física del dinero se realiza fuera del sistema y la operación queda auditada.</t>
+  </si>
+  <si>
+    <t>Agrega CA4: se conservan las asociaciones con apoderados. Agrega devolución de saldo (retiro o cambio de colegio): entrega manual, registro obligatorio.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un Apoderado autenticado, cuando ingresa a Mis alumnos, entonces solo visualiza los alumnos asociados a su cuenta. CA2: Dado cada alumno, cuando se muestra, entonces visualiza su nombre completo (compuesto desde primer nombre, segundo nombre, primer apellido y segundo apellido), curso y RUT enmascarado. CA3: Dado alumnos inactivos con historial, cuando corresponda, entonces se muestran solo para consulta histórica y sin acciones nuevas.</t>
+  </si>
+  <si>
+    <t>Nombre completo compuesto desde campos atomizados.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un proveedor válido, cuando se registra, entonces queda disponible para nuevas órdenes de compra. CA2: Dado un proveedor con historial, cuando deja de utilizarse, entonces se inactiva sin eliminar sus compras anteriores. CA3: Dado el contacto del proveedor, cuando se registra, entonces se guardan por separado primer nombre, segundo nombre (opcional), primer apellido, segundo apellido (opcional), correo y teléfono.</t>
+  </si>
+  <si>
+    <t>Contacto del proveedor con nombre atomizado.</t>
+  </si>
+  <si>
+    <t>Registrar la recepción de mercadería con sus facturas</t>
+  </si>
+  <si>
+    <t>ingresar al stock solo mercadería respaldada por facturas que coinciden</t>
+  </si>
+  <si>
+    <t>CA1: Dado una OC vigente, cuando llega mercadería con una o más facturas, entonces el Encargado registra cada factura (número, fecha, neto, IVA, total y sus líneas de producto, entre 1 y 60) y compara producto y cantidad contra la OC y las facturas. CA2: Dado que la suma de las cantidades facturadas por producto coincide exactamente con lo recibido, cuando confirma, entonces la recepción queda ACEPTADA como COMPLETA o INCOMPLETA, aumenta el stock físico por las unidades recibidas y se recalcula el CPP. CA3: Dado que las facturas no coinciden con la mercadería recibida o contienen artículos no ordenados, cuando se revisa, entonces la recepción puntual queda RECHAZADA con motivo obligatorio (junto con todas sus facturas), no modifica stock ni CPP, y la OC permanece vigente para un nuevo despacho. CA4: Dado una recepción INCOMPLETA aceptada, cuando quedan unidades pendientes, entonces la OC queda en RECEPCIÓN_PARCIAL y abierta para nuevas recepciones. CA5: Dado una OC con varias recepciones, cuando se consulta, entonces cada recepción muestra sus facturas, y cada factura aceptada queda pendiente de pago en Finanzas (se paga completa, sin pagos parciales).</t>
+  </si>
+  <si>
+    <t>Fusiona ex-HU50 y ex-HU53. Regla: 1 factura por recepción; rechazo puntual de recepción/factura manteniendo la OC vigente; múltiples recepciones/facturas por OC. Una recepción puede traer 1..* facturas (p. ej. límite de 60 ítems por factura del SII).</t>
+  </si>
+  <si>
+    <t>CA1: Dado movimientos financieros, cuando se consulta la cartola, entonces muestra fecha, tipo, referencia, monto y saldo. CA2: Dado el rol Autorizador, cuando consulta, entonces el acceso es de solo lectura salvo sus acciones de autorización. CA3: Dado abonos, pagos de facturas y devoluciones de saldo, cuando se registran, entonces aparecen una sola vez en la cartola y no se duplican por la venta/consumo del saldo.</t>
+  </si>
+  <si>
+    <t>Registra devoluciones de saldo en cartola de caja.</t>
+  </si>
+  <si>
+    <t>CA1: Dado un rango de fechas, cuando consulta reportes, entonces puede visualizar abonos, consumos/ventas, devoluciones de venta, devoluciones de saldo, pagos y otros indicadores definidos. CA2: Dado reportes, cuando se muestran, entonces distinguen movimientos de saldo de movimientos de caja para evitar doble contabilización. CA3: Dado información disponible, cuando se solicita, entonces se presentan gráficos/resúmenes sin alterar los datos fuente.</t>
+  </si>
+  <si>
+    <t>Distingue devoluciones de venta y de saldo en reportes.</t>
+  </si>
 </sst>
 </file>
 
@@ -29260,13 +29320,15 @@
         <v>42</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>67</v>
+        <v>456</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>457</v>
+      </c>
       <c r="M4" s="6"/>
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
@@ -29303,13 +29365,15 @@
         <v>42</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>74</v>
+        <v>458</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+      <c r="L5" s="4" t="s">
+        <v>459</v>
+      </c>
       <c r="M5" s="6"/>
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
@@ -29737,14 +29801,14 @@
         <v>42</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>417</v>
+        <v>460</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
@@ -29870,14 +29934,14 @@
         <v>42</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>425</v>
+        <v>462</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4" t="s">
-        <v>426</v>
+        <v>463</v>
       </c>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
@@ -29915,13 +29979,15 @@
         <v>42</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>138</v>
+        <v>464</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
+      <c r="L19" s="4" t="s">
+        <v>465</v>
+      </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
@@ -31090,13 +31156,15 @@
         <v>42</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>278</v>
+        <v>466</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
+      <c r="L46" s="4" t="s">
+        <v>467</v>
+      </c>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
       <c r="O46" s="6"/>
@@ -31203,7 +31271,7 @@
         <v>46</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>192</v>
@@ -31212,7 +31280,7 @@
         <v>445</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>23</v>
@@ -31221,14 +31289,14 @@
         <v>42</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4" t="s">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
@@ -31352,13 +31420,15 @@
         <v>42</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>319</v>
+        <v>472</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
+      <c r="L52" s="4" t="s">
+        <v>473</v>
+      </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
       <c r="O52" s="6"/>
@@ -31524,13 +31594,15 @@
         <v>42</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>340</v>
+        <v>474</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
+      <c r="L56" s="4" t="s">
+        <v>475</v>
+      </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
       <c r="O56" s="6"/>
